--- a/SV_annotsv_JVM/examples/column_description.xlsx
+++ b/SV_annotsv_JVM/examples/column_description.xlsx
@@ -1,45 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kjxz732/Hackathon_SVs/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF434156-CF3C-C043-B693-588F757F8446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{3D3A64CB-F96D-4D47-B454-95598A4885DD}"/>
+    <workbookView windowWidth="19095" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t>Column Names</t>
   </si>
@@ -47,262 +22,294 @@
     <t>Description</t>
   </si>
   <si>
+    <t>AnnotSV_ID</t>
+  </si>
+  <si>
+    <t>ID of TR</t>
+  </si>
+  <si>
     <t>SV_chrom</t>
   </si>
   <si>
+    <t>Chromosome of Tandem duplication (TR)</t>
+  </si>
+  <si>
     <t>SV_start</t>
   </si>
   <si>
+    <t>Coordinate start</t>
+  </si>
+  <si>
     <t>SV_end</t>
   </si>
   <si>
+    <t>Coordinate End</t>
+  </si>
+  <si>
+    <t>SV_type</t>
+  </si>
+  <si>
+    <t>Structural variant type, such as INS, DUP, DEL, INV, or BND.</t>
+  </si>
+  <si>
     <t>SV_length</t>
   </si>
   <si>
+    <t>TR length</t>
+  </si>
+  <si>
     <t>REF</t>
   </si>
   <si>
+    <t>Coordinate in reference</t>
+  </si>
+  <si>
     <t>ALT</t>
   </si>
   <si>
+    <t>TR string</t>
+  </si>
+  <si>
     <t>Gene_name</t>
   </si>
   <si>
+    <t>Symbol of overlapped genes with the SV</t>
+  </si>
+  <si>
     <t>Location</t>
   </si>
   <si>
+    <t>SV location in the gene’s Values: txStart, txEnd, exon’i’, intron’i’ e.g. « txStart-exon3 »</t>
+  </si>
+  <si>
     <t>Location2</t>
   </si>
   <si>
+    <t>SV location in the gene’s coding regions Values: UTR (no CDS in the gene), 5’UTR (before the CDS start), 3’UTR (after the CDS end), CDS (between the CDS start and the CDS end, can be in an exon or an intron).</t>
+  </si>
+  <si>
     <t>Tx</t>
   </si>
   <si>
+    <t>Transcript symbol</t>
+  </si>
+  <si>
     <t>Overlapped_tx_length</t>
   </si>
   <si>
+    <t>Length of the transcript (bp) overlapping with the SV</t>
+  </si>
+  <si>
     <t>Overlapped_CDS_percent</t>
   </si>
   <si>
+    <t>% of the CDS (bp overlapped with the SV)</t>
+  </si>
+  <si>
     <t>Frameshift</t>
   </si>
   <si>
+    <t>Indicates the frameshift status (yes, no, NA)</t>
+  </si>
+  <si>
     <t>RE_gene</t>
   </si>
   <si>
+    <t>Name of the genes regulated by a regulatory element overlapped with the SV to annotate. When available, the regulated gene name is detailed with associated haploinsufficiency (HI), triplosensitivity (TS), Exomiser (EX) scores, OMIM and candidate genes</t>
+  </si>
+  <si>
     <t>P_gain_source</t>
   </si>
   <si>
+    <t>Origin of the pathogenic gain genomic regions completely overlapped with the SV to annotate: dbVarNR (dbVar), ClinVar (CLN), ClinGen (TS3)</t>
+  </si>
+  <si>
+    <t>B_gain_source</t>
+  </si>
+  <si>
+    <t>Origin of the benign gain genomic regions completely overlapping the SV to annotate: gnomAD, ClinVar (CLN), ClinGen (TS40), DGV (dgv, nsv or esv), DDD, 1000 genomes (1000g), Ira M. Hall’s lab (IMH), Children’s Mercy Research Institute (CMRI)</t>
+  </si>
+  <si>
     <t>TAD_coordinate</t>
   </si>
   <si>
-    <t>REPEAT_type_left</t>
-  </si>
-  <si>
-    <t>REPEAT_type_right</t>
+    <t>Coordinates of the TAD whose boundaries overlapped with the annotated SV (boundaries included in the coordinates)</t>
+  </si>
+  <si>
+    <t>Repeat_type_left</t>
+  </si>
+  <si>
+    <t>Repeats type around the left SV breakpoint (+/- 100bp) e.g. AluSp, L2b, L1PA2, LTR12C, SVA</t>
+  </si>
+  <si>
+    <t>Repeat_type_right</t>
+  </si>
+  <si>
+    <t>Repeats type around the right SV breakpoint (+/- 100bp) e.g. AluSp, L2b, L1PA2, LTR12C, SVA_D</t>
   </si>
   <si>
     <t>SegDup_left</t>
   </si>
   <si>
+    <t>Segmental Duplication regions coordinates around the left SV breakpoint (+/- 100bp)</t>
+  </si>
+  <si>
     <t>SegDup_right</t>
   </si>
   <si>
+    <t>Segmental Duplication regions coordinates around the right SV breakpoint (+/- 100bp)</t>
+  </si>
+  <si>
     <t>ACMG</t>
   </si>
   <si>
+    <t>ACMG genes</t>
+  </si>
+  <si>
     <t>HI</t>
   </si>
   <si>
+    <t>ClinGen Haploinsufficiency Score</t>
+  </si>
+  <si>
     <t>TS</t>
   </si>
   <si>
+    <t>ClinGen Triplosensitivity Score</t>
+  </si>
+  <si>
     <t>DDD_HI_percent</t>
   </si>
   <si>
+    <t>Haploinsufficiency ranks from Deciphering Developmental Disorders (DDD)</t>
+  </si>
+  <si>
     <t>ExAC_dupZ</t>
   </si>
   <si>
-    <t>ExAC_cnv2</t>
+    <t>Positive dupZ_ExAC (Z score) from ExAC indicate gene intolerance to duplication</t>
+  </si>
+  <si>
+    <t>ExAC_cnvZ</t>
+  </si>
+  <si>
+    <t>Positive cnvZ_ExAC (Z score) from ExAC indicate gene intolerance to CNV</t>
   </si>
   <si>
     <t>LOEUF_bin</t>
   </si>
   <si>
+    <t>Minimal “decile bin of LOEUF” for given transcripts of a gene (lower values indicate more constrained) Values = integer [0-9]</t>
+  </si>
+  <si>
     <t>GnomAD_pLI</t>
   </si>
   <si>
+    <t>Score computed by gnomAD indicating the probability that a gene is intolerant to a loss of function variation (Nonsense, splice acceptor/donor variants due to SNV/indel</t>
+  </si>
+  <si>
     <t>ExAC_pLI</t>
   </si>
   <si>
+    <t>Score computed by ExAC indicating the probability that a gene is intolerant to a loss of function variation (Nonsense, splice acceptor/donor variants due to SNV/indel). ExAC considers pLI&gt;=0.9 as an extremely LoF intolerant gene</t>
+  </si>
+  <si>
     <t>Exomiser_gene_pheno_score</t>
   </si>
   <si>
-    <t>PhenoGenius_score</t>
-  </si>
-  <si>
-    <t>PhenoGenius_phenotype</t>
+    <t>Exomiser score for how close each overlapped gene is to the phenotype</t>
+  </si>
+  <si>
+    <t>PhenoGenius_gene_scores</t>
+  </si>
+  <si>
+    <t>Semicolon-separated NCBI gene IDs and their PhenoGenius scores, formatted as gene_id:score.</t>
+  </si>
+  <si>
+    <t>PhenoGenius_gene_specificity</t>
+  </si>
+  <si>
+    <t>Semicolon-separated NCBI gene IDs and phenotype specificity categories, formatted as gene_id:A/B/C/D.</t>
+  </si>
+  <si>
+    <t>PhenoGenius_best_gene</t>
+  </si>
+  <si>
+    <t>Gene symbol with the highest PhenoGenius score for the SV.</t>
+  </si>
+  <si>
+    <t>PhenoGenius_best_score</t>
+  </si>
+  <si>
+    <t>Highest PhenoGenius score among the genes associated with the SV.</t>
+  </si>
+  <si>
+    <t>PhenoGenius_best_specificity</t>
+  </si>
+  <si>
+    <t>Specificity category (A, B, C, or D) for the highest-scoring gene.</t>
   </si>
   <si>
     <t>GenCC_disease</t>
   </si>
   <si>
+    <t>GenCC disease name: e.g. Nizon-Isidor syndrome</t>
+  </si>
+  <si>
     <t>GenCC_classification</t>
   </si>
   <si>
+    <t>GenCC classification (Definitive, Strong, Moderate, Limited, Disputed, Animal Model Only, Refuted or No known disease relationship)</t>
+  </si>
+  <si>
     <t>Human_pheno_evidence</t>
   </si>
   <si>
+    <t>Phenotypic evidence from Human model</t>
+  </si>
+  <si>
     <t>AnnotSV_ranking_criteria</t>
   </si>
   <si>
+    <t>Decision criteria explaining the AnnotSV ranking score</t>
+  </si>
+  <si>
     <t>AnnotSV_ranking_score</t>
   </si>
   <si>
+    <t>SV ranking score following the 2019 joint consensus recommendation of ACMG and ClinGen. Scoring: pathogenic ≥0.99, likely pathogenic [0.90;0.98], variant of uncertain significance [0.89;-0.89], likely benign [-0.90;-0.98], benign ≤-0.99.</t>
+  </si>
+  <si>
     <t>ACMG_class</t>
   </si>
   <si>
-    <t>Chromosome of Tandem duplication (TR)</t>
-  </si>
-  <si>
-    <t>Coordinate start</t>
-  </si>
-  <si>
-    <t>Coordinate End</t>
-  </si>
-  <si>
-    <t>TR length</t>
-  </si>
-  <si>
-    <t>Coordinate in reference</t>
-  </si>
-  <si>
-    <t>TR string</t>
-  </si>
-  <si>
-    <t>Symbol of overlapped genes with the SV</t>
-  </si>
-  <si>
-    <t>SV location in the gene’s Values: txStart, txEnd, exon’i’, intron’i’ e.g. « txStart-exon3 »</t>
-  </si>
-  <si>
-    <t>SV location in the gene’s coding regions Values: UTR (no CDS in the gene), 5’UTR (before the CDS start), 3’UTR (after the CDS end), CDS (between the CDS start and the CDS end, can be in an exon or an intron).</t>
-  </si>
-  <si>
-    <t>Transcript symbol</t>
-  </si>
-  <si>
-    <t>Length of the transcript (bp) overlapping with the SV</t>
-  </si>
-  <si>
-    <t>% of the CDS (bp overlapped with the SV)</t>
-  </si>
-  <si>
-    <t>Indicates the frameshift status (yes, no, NA)</t>
-  </si>
-  <si>
-    <t>Name of the genes regulated by a regulatory element overlapped with the SV to annotate. When available, the regulated gene name is detailed with associated haploinsufficiency (HI), triplosensitivity (TS), Exomiser (EX) scores, OMIM and candidate genes</t>
-  </si>
-  <si>
-    <t>B_gain_source</t>
-  </si>
-  <si>
-    <t>Origin of the benign gain genomic regions completely overlapping the SV to annotate: gnomAD, ClinVar (CLN), ClinGen (TS40), DGV (dgv, nsv or esv), DDD, 1000 genomes (1000g), Ira M. Hall’s lab (IMH), Children’s Mercy Research Institute (CMRI)</t>
-  </si>
-  <si>
-    <t>Origin of the pathogenic gain genomic regions completely overlapped with the SV to annotate: dbVarNR (dbVar), ClinVar (CLN), ClinGen (TS3)</t>
-  </si>
-  <si>
-    <t>Coordinates of the TAD whose boundaries overlapped with the annotated SV (boundaries included in the coordinates)</t>
-  </si>
-  <si>
-    <t>Repeats type around the left SV breakpoint (+/- 100bp) e.g. AluSp, L2b, L1PA2, LTR12C, SVA</t>
-  </si>
-  <si>
-    <t>Repeats type around the right SV breakpoint (+/- 100bp) e.g. AluSp, L2b, L1PA2, LTR12C, SVA_D</t>
-  </si>
-  <si>
-    <t>Segmental Duplication regions coordinates around the left SV breakpoint (+/- 100bp)</t>
-  </si>
-  <si>
-    <t>Segmental Duplication regions coordinates around the right SV breakpoint (+/- 100bp)</t>
-  </si>
-  <si>
-    <t>ACMG genes</t>
-  </si>
-  <si>
-    <t>ClinGen Haploinsufficiency Score</t>
-  </si>
-  <si>
-    <t>ClinGen Triplosensitivity Score</t>
-  </si>
-  <si>
-    <t>Haploinsufficiency ranks from Deciphering Developmental Disorders (DDD)</t>
-  </si>
-  <si>
-    <t>Positive dupZ_ExAC (Z score) from ExAC indicate gene intolerance to duplication</t>
-  </si>
-  <si>
-    <t>Positive cnvZ_ExAC (Z score) from ExAC indicate gene intolerance to CNV</t>
-  </si>
-  <si>
-    <t>Minimal “decile bin of LOEUF” for given transcripts of a gene (lower values indicate more constrained) Values = integer [0-9]</t>
-  </si>
-  <si>
-    <t>Score computed by gnomAD indicating the probability that a gene is intolerant to a loss of function variation (Nonsense, splice acceptor/donor variants due to SNV/indel</t>
-  </si>
-  <si>
-    <t>Score computed by ExAC indicating the probability that a gene is intolerant to a loss of function variation (Nonsense, splice acceptor/donor variants due to SNV/indel). ExAC considers pLI&gt;=0.9 as an extremely LoF intolerant gene</t>
-  </si>
-  <si>
-    <t>Exomiser score for how close each overlapped gene is to the phenotype</t>
-  </si>
-  <si>
-    <t>Association score between “Symptom/Phenotype” and Gene. measures how well the patient’s phenotype matches a gene’s known disease associations. It is useful for gene and variant prioritization, larger values stronger associations.</t>
-  </si>
-  <si>
-    <t>PhenoGenius_specificity</t>
-  </si>
-  <si>
-    <t>Phenotype specificity into one of "A", "B", "C", "D" or “”: A - the reported phenotype is highly specific and relatively unique to the gene (top 40, 50% of diagnosis in PhenoGenius cohort). B - the reported phenotype is consistent with the gene, is highly specific, but not necessarily unique to the gene (top 250, 75% of diagnosis in PhenoGenius cohort). C - the phenotype is reported with limited association with the gene, not highly specific and/or with high genetic heterogeneity. D - the reported phenotype is NOT consistent with what is expected for the gene/genomic region or not consistent in general. “” - NO reported phenotype</t>
-  </si>
-  <si>
-    <t>Reported phenotype implicated in the association score</t>
-  </si>
-  <si>
-    <t>GenCC disease name: e.g. Nizon-Isidor syndrome</t>
-  </si>
-  <si>
-    <t>GenCC classification (Definitive, Strong, Moderate, Limited, Disputed, Animal Model Only, Refuted or No known disease relationship)</t>
-  </si>
-  <si>
-    <t>Phenotypic evidence from Human model</t>
-  </si>
-  <si>
-    <t>Decision criteria explaining the AnnotSV ranking score</t>
-  </si>
-  <si>
-    <t>SV ranking score following the 2019 joint consensus recommendation of ACMG and ClinGen. Scoring: pathogenic ≥0.99, likely pathogenic [0.90;0.98], variant of uncertain significance [0.89;-0.89], likely benign [-0.90;-0.98], benign ≤-0.99.</t>
-  </si>
-  <si>
     <t>SV ranking class into 1 of 5: class 1 (benign) class 2 (likely benign) class 3 (variant of unknown significance) class 4 (likely pathogenic) class 5 (pathogenic) class NA (Non Attributed)</t>
-  </si>
-  <si>
-    <t>AnnotSV_ID</t>
-  </si>
-  <si>
-    <t>ID of TR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,25 +317,356 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -336,26 +674,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -404,7 +1028,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -437,26 +1061,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -489,23 +1096,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -667,361 +1257,381 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E1DDC0F-FF81-BF46-9F0E-9C55DAB153DE}">
-  <dimension ref="A1:B42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B45"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="28.1640625" customWidth="1"/>
+    <col min="1" max="1" width="28.162962962963" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>82</v>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B21" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B22" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="B23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B24" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="B25" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B26" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="B27" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="28" spans="1:2">
+      <c r="A28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="B29" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="30" spans="1:2">
+      <c r="A30" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="B30" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="31" spans="1:2">
+      <c r="A31" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="B31" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="32" spans="1:2">
+      <c r="A32" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="B32" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
+    <row r="33" spans="1:2">
+      <c r="A33" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="B33" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
+    <row r="34" spans="1:2">
+      <c r="A34" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="B34" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="35" spans="1:2">
+      <c r="A35" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="B35" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" t="s">
+    <row r="36" spans="1:2">
+      <c r="A36" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="B36" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="37" spans="1:2">
+      <c r="A37" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
+      <c r="B37" t="s">
         <v>73</v>
       </c>
-      <c r="B35" t="s">
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="B38" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" t="s">
+    <row r="39" spans="1:2">
+      <c r="A39" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="40" spans="1:2">
+      <c r="A40" s="2" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="B40" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>38</v>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>39</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>